--- a/decks/bomme-studio/keyword-research.xlsx
+++ b/decks/bomme-studio/keyword-research.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Article Plan" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Keyword Universe" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Excluded" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Read Me" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Striking Distance (GSC)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Read Me" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20358,7 +20359,5171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:E301"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Query (verified ranking)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Avg Position</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions / mo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks / mo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>In 90-Day Plan?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>what is tencel</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2803</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>783</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tencel</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>756</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tencel fabric</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>669</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>private label clothing</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>548</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>private label apparel</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>475</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tech pack</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>429</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>382</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturer</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>streetwear clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tech packs</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fashion ecommerce agency</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>what is tencil fabric</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>white label vs private label</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>clothing streetwear</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>private label vs white label</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>273</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>leading global fashion directory</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>streetwear manufacturer</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>hemp fabric</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>custom clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>private vs white label</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>custom streetwear manufacturer</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>loungewear manufacturer</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>216</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturers usa</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>what is tencil</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>white label versus private label</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tech pack fashion</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>188</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>underwear manufacturer</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>clothing tech pack</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>custom clothing manufacturer</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>175</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>what is white label vs private label</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>difference between white label and private label</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>171</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>what is private label vs white label</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>private label clothing supplier</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>private label activewear manufacturer</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>private label versus white label</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>tech packs for clothing</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>what fabric is tencel</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>garment dyed</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>streetwear clothing manufacturer</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>white label clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>luxury blanks</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>141</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>tencel material</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>private label fitness apparel</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>private label athletic apparel manufacturers</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>private label clothing suppliers</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>133</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>fashion production</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>131</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>white label and private label</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>luxury blank hoodies</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>startup fashion tech pack</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>white vs private label</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>fully fashioned knitwear</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>difference between private label and white label</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>private label activewear</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>private label workout clothing</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>private label workout clothes</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>white label private label</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>white label or private label</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>best private label clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>custom underwear manufacturers</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>clothing manufacturers streetwear</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>start a clothing line</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>private label athletic wear</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>what is tencel made of</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>underwear manufacturers</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>what is tencel lyocell</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>tech pack clothing</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>fashion tech pack</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>102</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>is tencel breathable</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>private label apparel manufacturers usa</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>kinds of pants</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>what is a tech pack</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>sample maker los angeles</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>private label sportswear</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>private label clothing wholesalers</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>private clothing</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>private label garments</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>custom private label clothing</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>whats tencel</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>luxury blanks wholesale</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>high quality custom clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>apparel prototyping</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>clothing sample developers</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>private label apparel manufacturer</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturers los angeles</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>what is tech pack</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>how to create a tech pack</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>what is hemp fabric</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>t shirt tech pack</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>private label yoga pants</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>best brands on pinterest</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>brand manufacturing services</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>merchandise manufacturers</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>custom clothing manufacturers usa</t>
+        </is>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>streetwear blanks</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>custom boxer briefs manufacturers</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>premium blanks wholesale</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>clothing sample makers los angeles</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>wholesale streetwear blanks</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>private label streetwear manufacturer</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cut and sew manufacturers los angeles</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>apparel tech pack</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>clothing manufacturers in usa</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>private labeling vs white labeling</t>
+        </is>
+      </c>
+      <c r="B105" s="6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>what is the difference between white label and private label</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>white labeling vs private labeling</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>clothing prototyping</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>how to design t shirts</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>activewear manufacturers in los angeles</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>tercel fabric</t>
+        </is>
+      </c>
+      <c r="B111" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>streetwear blanks wholesale</t>
+        </is>
+      </c>
+      <c r="B112" s="6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>sewing factory los angeles</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cmt manufacturing</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>private label wholesale clothing</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>what is a white label</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>clothing manufacturers usa</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>500 gsm</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>bomme studio reviews</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>luxury blank t shirts</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>clothes manufacturer</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>manufactured clothing</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>private label shirt manufacturers</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>private label athleisure</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>dress manufacturers</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturers in los angeles</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>what is a tech pack in fashion</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>private label garment manufacturing</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>garment tech pack</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>clothing makers</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>tensel fabric</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>pattern maker los angeles</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>tech pack for clothing brand</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>private label wholesale clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>usa clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>what is tencel material</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>luxury hoodie blanks</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>private label tracksuit</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>private label yoga clothing</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>sewing factory los angeles ca</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>private label apparel fulfillment</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>how to launch a clothing line</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>los angeles sewing factory</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>private label t shirt manufacturers</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>tech pack for garment</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>tech pack maker</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>private label jacket manufacturers</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>private label wholesale apparel</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>t shirt profit margin</t>
+        </is>
+      </c>
+      <c r="B149" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>private label clothing wholesale</t>
+        </is>
+      </c>
+      <c r="B150" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturer usa</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>private label yoga wear</t>
+        </is>
+      </c>
+      <c r="B152" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>tencil fabric</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>unique custom merch</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>technical pack</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>luxury streetwear blanks wholesale</t>
+        </is>
+      </c>
+      <c r="B156" s="6" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>custom full service manufacturer</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>luxury streetwear blanks</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>start clothing line</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>athletic wear manufacturers los angeles</t>
+        </is>
+      </c>
+      <c r="B160" s="6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>quality control in clothing industry</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>activewear manufacturer los angeles</t>
+        </is>
+      </c>
+      <c r="B162" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>private label athletic wear usa</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>custom streetwear</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>garment measurement</t>
+        </is>
+      </c>
+      <c r="B165" s="6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>how to make tech packs</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>full package manufacturing los angeles</t>
+        </is>
+      </c>
+      <c r="B167" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>manufacturing clothes</t>
+        </is>
+      </c>
+      <c r="B168" s="6" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>private white label</t>
+        </is>
+      </c>
+      <c r="B169" s="6" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>clothing private label</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>private label gym wear</t>
+        </is>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>private label manufacturers for clothing</t>
+        </is>
+      </c>
+      <c r="B172" s="6" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>private brand</t>
+        </is>
+      </c>
+      <c r="B173" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>quality control in apparel industry</t>
+        </is>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>street wear clothing</t>
+        </is>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>white label athletic wear</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>white label clothes</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>clothing sample makers</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>private label dress manufacturers</t>
+        </is>
+      </c>
+      <c r="B179" s="6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>brand manufacturing</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>luxury wholesale blanks</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>mens underwear manufacturers</t>
+        </is>
+      </c>
+      <c r="B182" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>private label apparel supplier</t>
+        </is>
+      </c>
+      <c r="B183" s="6" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>private label clothing vendors</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>white label clothing manufacturer</t>
+        </is>
+      </c>
+      <c r="B185" s="6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>what does white label mean</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>how to start a fashion line</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>clothing manufacturer los angeles ca</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>garment manufacturing los angeles</t>
+        </is>
+      </c>
+      <c r="B189" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>private clothing brands</t>
+        </is>
+      </c>
+      <c r="B190" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>private label apparel manufacturers in usa</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>us clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B192" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C192" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D192" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>garment techpack</t>
+        </is>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D193" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>streetwear supplier</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D194" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>luxury clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B195" s="6" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>quality control in garment production</t>
+        </is>
+      </c>
+      <c r="B196" s="5" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D196" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>garment contractors los angeles</t>
+        </is>
+      </c>
+      <c r="B197" s="5" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="C197" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D197" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>private label women's clothing</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="C198" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D198" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>tencil</t>
+        </is>
+      </c>
+      <c r="B199" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>top clothing manufacturers in los angeles</t>
+        </is>
+      </c>
+      <c r="B200" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>mens underwear manufacturer</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>private label loungewear</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="C202" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D202" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>private label clothing usa</t>
+        </is>
+      </c>
+      <c r="B203" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C203" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D203" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>los angeles garment contractors</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C204" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D204" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>margins and markups fashion</t>
+        </is>
+      </c>
+      <c r="B205" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>clothing production companies</t>
+        </is>
+      </c>
+      <c r="B206" s="5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>whitelabel sneakers</t>
+        </is>
+      </c>
+      <c r="B207" s="6" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>apparel manufacturers</t>
+        </is>
+      </c>
+      <c r="B208" s="5" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="C208" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D208" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>apparel sample maker</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="C209" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D209" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>clothing production company</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="C210" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D210" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>streetwear wholesale blanks</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="C211" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D211" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>what is a techpack</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C212" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D212" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>manufacturers in los angeles</t>
+        </is>
+      </c>
+      <c r="B213" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C213" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D213" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>private label t shirt manufacturer usa</t>
+        </is>
+      </c>
+      <c r="B214" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C214" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D214" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>private label women's clothing manufacturer</t>
+        </is>
+      </c>
+      <c r="B215" s="6" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="C215" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D215" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>apparel production</t>
+        </is>
+      </c>
+      <c r="B216" s="5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="C216" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D216" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>premium custom merch</t>
+        </is>
+      </c>
+      <c r="B217" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C217" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D217" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>clothes manufacturing</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="C218" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D218" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>small batch clothing manufacturers los angeles</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C219" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D219" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>garment product development studios</t>
+        </is>
+      </c>
+      <c r="B220" s="5" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="C220" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D220" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>how to price apparel for profit</t>
+        </is>
+      </c>
+      <c r="B221" s="5" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="C221" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D221" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>quality control apparel industry</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C222" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D222" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>sweats manufacturer</t>
+        </is>
+      </c>
+      <c r="B223" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="C223" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D223" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>private label women's clothing wholesale</t>
+        </is>
+      </c>
+      <c r="B224" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C224" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D224" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>tech pack format</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="C225" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D225" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>dyed</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C226" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D226" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>fashion ecommerce marketing agency</t>
+        </is>
+      </c>
+      <c r="B227" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C227" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D227" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>luxury clothing manufacturers usa</t>
+        </is>
+      </c>
+      <c r="B228" s="6" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C228" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D228" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>site:www.bommestudio.com</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C229" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D229" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>brand manufacturer</t>
+        </is>
+      </c>
+      <c r="B230" s="6" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="C230" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D230" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>private label loungewear manufacturer</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="C231" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D231" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>t shirt manufacturer</t>
+        </is>
+      </c>
+      <c r="B232" s="6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="C232" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="D232" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ai clothing design</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="C233" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D233" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>custom made underwear suppliers</t>
+        </is>
+      </c>
+      <c r="B234" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C234" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D234" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>custom streetwear clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B235" s="6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C235" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D235" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>difference between private and white label</t>
+        </is>
+      </c>
+      <c r="B236" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C236" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D236" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>los angeles california sewing factory</t>
+        </is>
+      </c>
+      <c r="B237" s="6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C237" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D237" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>underwear manufacturers usa</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C238" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D238" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>women's wear manufacturer</t>
+        </is>
+      </c>
+      <c r="B239" s="6" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="C239" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D239" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>difference between white label and private label products</t>
+        </is>
+      </c>
+      <c r="B240" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C240" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D240" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>fashion production support</t>
+        </is>
+      </c>
+      <c r="B241" s="6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C241" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D241" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>private label white label</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="C242" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D242" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>sewing company los angeles</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="C243" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D243" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>what is the difference between private label and white label</t>
+        </is>
+      </c>
+      <c r="B244" s="6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C244" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D244" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>wholesale private label clothing</t>
+        </is>
+      </c>
+      <c r="B245" s="6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="C245" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D245" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>design to sample services</t>
+        </is>
+      </c>
+      <c r="B246" s="6" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C246" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D246" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>private label clothing manufacturing</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="C247" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D247" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>private label fashion manufacturers</t>
+        </is>
+      </c>
+      <c r="B248" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="C248" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D248" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>contract manufactured, private label, special &amp;amp; custom clothing suppliers</t>
+        </is>
+      </c>
+      <c r="B249" s="6" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="C249" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D249" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>mexico import duties manufacturing</t>
+        </is>
+      </c>
+      <c r="B250" s="6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C250" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D250" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>usa private label clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B251" s="6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C251" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D251" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>white label vs.private label</t>
+        </is>
+      </c>
+      <c r="B252" s="6" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C252" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D252" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>clothing launch</t>
+        </is>
+      </c>
+      <c r="B253" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C253" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D253" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>custom clothing manufacturers in usa</t>
+        </is>
+      </c>
+      <c r="B254" s="6" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="C254" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D254" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>denim jacket manufacturer los angeles ca</t>
+        </is>
+      </c>
+      <c r="B255" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C255" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D255" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>different kinds of pants</t>
+        </is>
+      </c>
+      <c r="B256" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C256" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D256" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>private clothing manufacturers</t>
+        </is>
+      </c>
+      <c r="B257" s="6" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="C257" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D257" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>private label clothes</t>
+        </is>
+      </c>
+      <c r="B258" s="6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C258" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D258" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>quality control clothing</t>
+        </is>
+      </c>
+      <c r="B259" s="5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="C259" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D259" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>white label fitness clothing</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="C260" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D260" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>american made fitness clothing</t>
+        </is>
+      </c>
+      <c r="B261" s="5" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="C261" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D261" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>gsm hoodie</t>
+        </is>
+      </c>
+      <c r="B262" s="6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="C262" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D262" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>high end blanks</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C263" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D263" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>manufacturer los angeles</t>
+        </is>
+      </c>
+      <c r="B264" s="6" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C264" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D264" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>creating clothing line</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="C265" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D265" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>garment measurements</t>
+        </is>
+      </c>
+      <c r="B266" s="6" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="C266" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D266" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>immex duty free</t>
+        </is>
+      </c>
+      <c r="B267" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C267" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D267" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>private label clothing brands</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="C268" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D268" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>underwear manufacturer usa</t>
+        </is>
+      </c>
+      <c r="B269" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C269" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>clothing samples manufacturers</t>
+        </is>
+      </c>
+      <c r="B270" s="6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="C270" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>techpack</t>
+        </is>
+      </c>
+      <c r="B271" s="5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="C271" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>premium blanks</t>
+        </is>
+      </c>
+      <c r="B272" s="5" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="C272" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>designer denim manufacturer los angeles ca</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C273" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>nike white label</t>
+        </is>
+      </c>
+      <c r="B274" s="6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C274" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>t shirt manufacturers</t>
+        </is>
+      </c>
+      <c r="B275" s="6" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C275" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>fitness gear manufacturers</t>
+        </is>
+      </c>
+      <c r="B276" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="C276" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>private label shirt manufacturer</t>
+        </is>
+      </c>
+      <c r="B277" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C277" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>private label tshirts manufacturers</t>
+        </is>
+      </c>
+      <c r="B278" s="5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="C278" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>what's the difference between white label and private label</t>
+        </is>
+      </c>
+      <c r="B279" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C279" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>white label activewear</t>
+        </is>
+      </c>
+      <c r="B280" s="6" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="C280" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>la manufacturers</t>
+        </is>
+      </c>
+      <c r="B281" s="6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="C281" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>import tariffs manufacturing mexico</t>
+        </is>
+      </c>
+      <c r="B282" s="6" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C282" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>t shirt manufacturer private label</t>
+        </is>
+      </c>
+      <c r="B283" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C283" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>blank streetwear</t>
+        </is>
+      </c>
+      <c r="B284" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C284" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>clothing prototype production</t>
+        </is>
+      </c>
+      <c r="B285" s="5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="C285" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>private label clothes manufacturer</t>
+        </is>
+      </c>
+      <c r="B286" s="6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="C286" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>white label clothing wholesale</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="C287" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>womens fashion clothing manufacturer</t>
+        </is>
+      </c>
+      <c r="B288" s="6" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C288" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>clothing manufacturers for small orders los angeles</t>
+        </is>
+      </c>
+      <c r="B289" s="6" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="C289" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>contract sewing los angeles</t>
+        </is>
+      </c>
+      <c r="B290" s="5" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="C290" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>clothing white label</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="C291" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>custom t shirt manufacturer</t>
+        </is>
+      </c>
+      <c r="B292" s="5" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="C292" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>factories in los angeles</t>
+        </is>
+      </c>
+      <c r="B293" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C293" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>fashion supply chain management</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C294" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>private label white label difference</t>
+        </is>
+      </c>
+      <c r="B295" s="6" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="C295" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>t shirt manufacturer los angeles</t>
+        </is>
+      </c>
+      <c r="B296" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C296" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>los angeles cut and sew manufacturers</t>
+        </is>
+      </c>
+      <c r="B297" s="6" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="C297" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>tencel textile</t>
+        </is>
+      </c>
+      <c r="B298" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C298" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>private label for clothing</t>
+        </is>
+      </c>
+      <c r="B299" s="6" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C299" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>custom streetwear clothing</t>
+        </is>
+      </c>
+      <c r="B300" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C300" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>streetwear wholesale manufacturers</t>
+        </is>
+      </c>
+      <c r="B301" s="5" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="C301" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E301" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20434,88 +25599,100 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" s="11" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Striking Distance (GSC)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Verified from your Search Console: queries where you already rank positions 11-30 with real impressions (top 300 by impressions). These are the fastest wins, optimization on existing pages rather than new articles.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr"/>
+      <c r="B9" s="11" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>How to read the colors</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Pillar</t>
-        </is>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Gold = Activewear &amp; Performance · Blue = Premium Basics &amp; Full-Package · Tan = Custom Merch &amp; Branded Apparel.</t>
-        </is>
-      </c>
+      <c r="B10" s="11" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>KD (difficulty)</t>
+          <t>Pillar</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Green = easy (under 30) · Yellow = moderate (30–49) · Red = hard (50+). Lower is faster to rank.</t>
+          <t>Gold = Activewear &amp; Performance · Blue = Premium Basics &amp; Full-Package · Tan = Custom Merch &amp; Branded Apparel.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
+          <t>KD (difficulty)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Green = easy (under 30) · Yellow = moderate (30–49) · Red = hard (50+). Lower is faster to rank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
           <t>Funnel</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>BoFu = decision-stage (find-a-manufacturer) · MoFu = comparison · ToFu = education.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr"/>
-      <c r="B13" s="11" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Why these pillars</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Strategy</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Recover the activewear authority you lost, own premium basics / full-package, and build custom merch as a second engine — all aimed at established brands with budgets, not low-MOQ startups.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
-      <c r="B16" s="11" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr"/>
+      <c r="B17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Next step</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Review the plan, then let's lock Month 1 and start production. Questions? Reply to the email this was shared from.</t>
         </is>
